--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2023_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2023_magallanes.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:54</t>
+    <t xml:space="preserve">2026-09-24 01:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -570,19 +570,19 @@
         <v>8</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>-0.45</v>
+        <v>0.47</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>-0.68</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="3">
@@ -593,19 +593,19 @@
         <v>8</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.34</v>
+        <v>0.79</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.05</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="4">
@@ -616,19 +616,19 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>-0.4</v>
+        <v>-0.17</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.23</v>
+        <v>0.18</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>-0.64</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="5">
@@ -639,19 +639,19 @@
         <v>8</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.29</v>
+        <v>0.56</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.11</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.49</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="6">
@@ -662,19 +662,19 @@
         <v>8</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>-0.39</v>
+        <v>-0.58</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.27</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="7">
@@ -708,7 +708,7 @@
         <v>5</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>328</v>
@@ -727,7 +727,7 @@
         <v>5</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>328</v>
@@ -746,7 +746,7 @@
         <v>5</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.16</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>328</v>
@@ -765,7 +765,7 @@
         <v>5</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.15</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>328</v>
@@ -784,7 +784,7 @@
         <v>5</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-0.48</v>
+        <v>-0.42</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>328</v>
@@ -803,7 +803,7 @@
         <v>5</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-0.43</v>
+        <v>-0.38</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>328</v>
@@ -822,7 +822,7 @@
         <v>5</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.22</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>328</v>
@@ -841,7 +841,7 @@
         <v>5</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.15</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>328</v>
@@ -860,7 +860,7 @@
         <v>5</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>328</v>
@@ -879,7 +879,7 @@
         <v>5</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.23</v>
+        <v>0.14</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>328</v>
@@ -894,19 +894,19 @@
         <v>26</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="19">
@@ -921,7 +921,7 @@
         <v>5</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.16</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>328</v>
@@ -940,7 +940,7 @@
         <v>5</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.21</v>
+        <v>0.11</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>328</v>
@@ -955,19 +955,19 @@
         <v>31</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.65</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.37</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="22">
@@ -978,19 +978,19 @@
         <v>31</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.66</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.36</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="23">
@@ -1001,19 +1001,19 @@
         <v>31</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.44</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>-0.22</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.01</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="24">
@@ -1024,19 +1024,19 @@
         <v>31</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>345</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="25">
@@ -1047,19 +1047,19 @@
         <v>31</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>0.29</v>
+        <v>0.46</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>0.35</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-0.06</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="26">
@@ -1070,19 +1070,19 @@
         <v>31</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>-0.7</v>
+        <v>-0.45</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.14</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-0.63</v>
+        <v>-0.31</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2023_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2023_magallanes.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:44</t>
+    <t xml:space="preserve">2026-10-01 23:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">plot_regional_correl_matriz_m_movinterna_a_2023_magallanes.png</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2023_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2023_magallanes.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:17</t>
+    <t xml:space="preserve">2026-10-05 20:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
